--- a/output/pdf_financials_xlsx/NCI.xlsx
+++ b/output/pdf_financials_xlsx/NCI.xlsx
@@ -973,22 +973,22 @@
         <v>1.411211</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.204264</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1.786608</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>2.610796</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>3.417226</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.075014</v>
+        <v>7.40131</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>5.364665</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0.160795</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.165782</v>
+        <v>0.196442</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.478193</v>
+        <v>-0.001378</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>1.024061</v>
@@ -2313,10 +2313,10 @@
         <v>0.949229</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.036776</v>
+        <v>3.067436</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>11.100959</v>
+        <v>10.621388</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>9.800796</v>
@@ -2378,10 +2378,10 @@
         <v>5.377363295110391</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>10.9519734066327</v>
+        <v>11.06254708893503</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>19.77837448670421</v>
+        <v>18.92393165604758</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>11.75850120079939</v>
@@ -8263,22 +8263,22 @@
         </is>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.00369</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046472</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09056</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-0.071011</v>
+        <v>-0.161588</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>-0.706355</v>
+        <v>-0.892015</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>-1.012008</v>
+        <v>-1.125091</v>
       </c>
     </row>
     <row r="125">
@@ -8328,22 +8328,22 @@
         </is>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.00369</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046472</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09056</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-0.071011</v>
+        <v>-0.161588</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>-0.706355</v>
+        <v>-0.892015</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>-1.012008</v>
+        <v>-1.125091</v>
       </c>
     </row>
     <row r="126">
@@ -31926,7 +31926,11 @@
           <t>Repayment of bank indebtedness (Note 16)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -37572,7 +37576,11 @@
           <t>Lease payment (Note 16)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -59384,7 +59392,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -63722,7 +63730,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -66492,7 +66500,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -72216,7 +72224,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">

--- a/output/pdf_financials_xlsx/NCI.xlsx
+++ b/output/pdf_financials_xlsx/NCI.xlsx
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>0.000354</v>
       </c>
     </row>
     <row r="113">
@@ -32536,7 +32536,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -33936,7 +33940,11 @@
           <t>Additions to intangible assets (Note 12)</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -35716,7 +35724,11 @@
           <t>(Additions) intangible assets (Note 15)</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -45010,7 +45022,11 @@
           <t>(Additions) Intangible assets (Note 16)</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NCI.xlsx
+++ b/output/pdf_financials_xlsx/NCI.xlsx
@@ -2909,46 +2909,46 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.036015</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.082214</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.061254</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.009542999999999999</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.009542999999999999</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.049511</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.008449999999999999</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.102464</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.06762899999999999</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.106438</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.473585</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>0.6700199999999999</v>
       </c>
     </row>
     <row r="41">
@@ -2970,46 +2970,46 @@
         <v>3.36494</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>3.091294</v>
+        <v>3.127309</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>4.162365</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>11.350745</v>
+        <v>11.432959</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>10.981806</v>
+        <v>11.04306</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.614075</v>
+        <v>5.623618</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>6.166032</v>
+        <v>6.175575</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.049511</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.008449999999999999</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>2.115072</v>
+        <v>2.241072</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>3.747046</v>
+        <v>3.84951</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>3.88152</v>
+        <v>3.949149</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>6.432724</v>
+        <v>6.539162</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>16.898548</v>
+        <v>17.372133</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>29.350268</v>
+        <v>30.020288</v>
       </c>
     </row>
     <row r="42">
@@ -3397,22 +3397,22 @@
         <v>0.025665</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.255094</v>
+        <v>0.219079</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.454049</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.248995</v>
+        <v>0.166781</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.361817</v>
+        <v>0.300563</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.237694</v>
+        <v>0.228151</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.258961</v>
+        <v>0.249418</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.127733</v>
+        <v>0.001733</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.12021</v>
+        <v>0.017746</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.104182</v>
+        <v>0.036553</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.130135</v>
+        <v>0.023697</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.29859</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.347157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4613,40 +4613,40 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.023405</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.07181999999999999</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.028356</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.016071</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.242356</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.184455</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.519251</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.033497</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.085949</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.276361</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.045702</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.174237</v>
       </c>
       <c r="Q67" s="3" t="n">
         <v>0</v>
@@ -4695,10 +4695,10 @@
         <v>3.885223</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.033497</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.085949</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>7.360079</v>
@@ -8176,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>-0.082986</v>
       </c>
       <c r="I123" s="3" t="n">
         <v>0</v>
@@ -8306,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.082986</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -30294,7 +30294,11 @@
           <t>Deferred income tax expense (Note 7)</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -43444,7 +43448,11 @@
           <t>(Decrease) in long-term debt (Note 18)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -52966,7 +52974,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
